--- a/Raw_Data/v7a_2050_clempn_exc_allecosys.xlsx
+++ b/Raw_Data/v7a_2050_clempn_exc_allecosys.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StefanÅström\C_Verktyg\Python\ALL_PYTHON\2026_v7_Goth_Prot_CBA\Raw_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B8C74EE5-7D50-4038-BDF6-F07A2DFF8BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12BA10E-0ECB-4991-92E5-A093C10F70AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-2730" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{59DF1989-4071-4D6D-9A8E-77AC20AF0877}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="11" xr2:uid="{59DF1989-4071-4D6D-9A8E-77AC20AF0877}"/>
   </bookViews>
   <sheets>
     <sheet name="clempn_exc_allecosys (11)" sheetId="11" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="clempn_exc_allecosys (3)" sheetId="2" r:id="rId9"/>
     <sheet name="clempn_exc_allecosys (2)" sheetId="3" r:id="rId10"/>
     <sheet name="clempn_exc_allecosys (1)" sheetId="4" r:id="rId11"/>
-    <sheet name="clempn_exc_allecosys" sheetId="1" r:id="rId12"/>
+    <sheet name="clempn_exc_allecosys (12)" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -34,9 +34,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="79">
   <si>
     <t>Eutrophication: Exceedance of Critical Loads (all ecosystems)</t>
-  </si>
-  <si>
-    <t>Scenario: LRTAP_Baseline_v7</t>
   </si>
   <si>
     <t xml:space="preserve">Region: </t>
@@ -268,6 +265,9 @@
   </si>
   <si>
     <t>Scenario: OPT Health -60 AAE -45 v7a</t>
+  </si>
+  <si>
+    <t>Scenario: Baseline_v7a</t>
   </si>
 </sst>
 </file>
@@ -1138,73 +1138,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>54.4</v>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>14.5</v>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>47.4</v>
@@ -1333,10 +1333,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>34.200000000000003</v>
@@ -1377,10 +1377,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>3.4</v>
@@ -1421,10 +1421,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>34.9</v>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>7.6</v>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>32.200000000000003</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>268.39999999999998</v>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>234.6</v>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>158.80000000000001</v>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>66.8</v>
@@ -1729,10 +1729,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>26.2</v>
@@ -1773,10 +1773,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>17.3</v>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>139</v>
@@ -1861,10 +1861,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.7</v>
@@ -1905,10 +1905,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>28.7</v>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.5</v>
@@ -1993,10 +1993,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -2037,10 +2037,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>11.4</v>
@@ -2081,10 +2081,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>117.3</v>
@@ -2125,10 +2125,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>45</v>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>96.9</v>
@@ -2213,10 +2213,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>24.1</v>
@@ -2257,10 +2257,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>13.4</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>235.1</v>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>357.4</v>
@@ -2389,7 +2389,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>2115.1</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>17.399999999999999</v>
@@ -2474,10 +2474,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>11.1</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>28.1</v>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>117.2</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>33.6</v>
@@ -2650,10 +2650,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>49.2</v>
@@ -2694,10 +2694,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>58.6</v>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>5.9</v>
@@ -2782,10 +2782,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>15.5</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>4.3</v>
@@ -2870,10 +2870,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>10.7</v>
@@ -2914,10 +2914,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>209.4</v>
@@ -2958,10 +2958,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>3323.8</v>
@@ -3002,10 +3002,10 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>33.200000000000003</v>
@@ -3046,10 +3046,10 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>22.3</v>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53">
         <v>310</v>
@@ -3134,10 +3134,10 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54">
         <v>147.69999999999999</v>
@@ -3178,10 +3178,10 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C55">
         <v>63.6</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C56">
         <v>4461.3999999999996</v>
@@ -3263,7 +3263,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57">
         <v>6576.5</v>
@@ -3319,73 +3319,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>54.4</v>
@@ -3426,10 +3426,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>14.5</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>47.4</v>
@@ -3514,10 +3514,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>34.200000000000003</v>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>3.4</v>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>34.9</v>
@@ -3646,10 +3646,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>7.6</v>
@@ -3690,10 +3690,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>32.200000000000003</v>
@@ -3734,10 +3734,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>268.39999999999998</v>
@@ -3778,10 +3778,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>234.6</v>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>158.80000000000001</v>
@@ -3866,10 +3866,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>66.8</v>
@@ -3910,10 +3910,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>26.2</v>
@@ -3954,10 +3954,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>17.3</v>
@@ -3998,10 +3998,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>139</v>
@@ -4042,10 +4042,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.7</v>
@@ -4086,10 +4086,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>28.7</v>
@@ -4130,10 +4130,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.5</v>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -4218,10 +4218,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>11.4</v>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>117.3</v>
@@ -4306,10 +4306,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>45</v>
@@ -4350,10 +4350,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>96.9</v>
@@ -4394,10 +4394,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>24.1</v>
@@ -4438,10 +4438,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>13.4</v>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>235.1</v>
@@ -4526,10 +4526,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>357.4</v>
@@ -4570,7 +4570,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>2115.1</v>
@@ -4611,10 +4611,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>17.399999999999999</v>
@@ -4655,10 +4655,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>11.1</v>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>28.1</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>117.2</v>
@@ -4787,10 +4787,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>33.6</v>
@@ -4831,10 +4831,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>49.2</v>
@@ -4875,10 +4875,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>58.6</v>
@@ -4919,10 +4919,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>5.9</v>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>15.5</v>
@@ -5007,10 +5007,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>4.3</v>
@@ -5051,10 +5051,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>10.7</v>
@@ -5095,10 +5095,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>209.4</v>
@@ -5139,10 +5139,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>3323.8</v>
@@ -5183,10 +5183,10 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>33.200000000000003</v>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>22.3</v>
@@ -5271,10 +5271,10 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53">
         <v>310</v>
@@ -5315,10 +5315,10 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54">
         <v>147.69999999999999</v>
@@ -5359,10 +5359,10 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C55">
         <v>63.6</v>
@@ -5403,7 +5403,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C56">
         <v>4461.3999999999996</v>
@@ -5444,7 +5444,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57">
         <v>6576.5</v>
@@ -5500,73 +5500,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>54.4</v>
@@ -5607,10 +5607,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>14.5</v>
@@ -5651,10 +5651,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>47.4</v>
@@ -5695,10 +5695,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>34.200000000000003</v>
@@ -5739,10 +5739,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>3.4</v>
@@ -5783,10 +5783,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>34.9</v>
@@ -5827,10 +5827,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>7.6</v>
@@ -5871,10 +5871,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>32.200000000000003</v>
@@ -5915,10 +5915,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>268.39999999999998</v>
@@ -5959,10 +5959,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>234.6</v>
@@ -6003,10 +6003,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>158.80000000000001</v>
@@ -6047,10 +6047,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>66.8</v>
@@ -6091,10 +6091,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>26.2</v>
@@ -6135,10 +6135,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>17.3</v>
@@ -6179,10 +6179,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>139</v>
@@ -6223,10 +6223,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.7</v>
@@ -6267,10 +6267,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>28.7</v>
@@ -6311,10 +6311,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.5</v>
@@ -6355,10 +6355,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -6399,10 +6399,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>11.4</v>
@@ -6443,10 +6443,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>117.3</v>
@@ -6487,10 +6487,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>45</v>
@@ -6531,10 +6531,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>96.9</v>
@@ -6575,10 +6575,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>24.1</v>
@@ -6619,10 +6619,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>13.4</v>
@@ -6663,10 +6663,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>235.1</v>
@@ -6707,10 +6707,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>357.4</v>
@@ -6751,7 +6751,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>2115.1</v>
@@ -6792,10 +6792,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>17.399999999999999</v>
@@ -6836,10 +6836,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>11.1</v>
@@ -6880,10 +6880,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>28.1</v>
@@ -6924,10 +6924,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>117.2</v>
@@ -6968,10 +6968,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>33.6</v>
@@ -7012,10 +7012,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>49.2</v>
@@ -7056,10 +7056,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>58.6</v>
@@ -7100,10 +7100,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>5.9</v>
@@ -7144,10 +7144,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>15.5</v>
@@ -7188,10 +7188,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>4.3</v>
@@ -7232,10 +7232,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>10.7</v>
@@ -7276,10 +7276,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>209.4</v>
@@ -7320,10 +7320,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>3323.8</v>
@@ -7364,10 +7364,10 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>33.200000000000003</v>
@@ -7408,10 +7408,10 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>22.3</v>
@@ -7452,10 +7452,10 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53">
         <v>310</v>
@@ -7496,10 +7496,10 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54">
         <v>147.69999999999999</v>
@@ -7540,10 +7540,10 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C55">
         <v>63.6</v>
@@ -7584,7 +7584,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C56">
         <v>4461.3999999999996</v>
@@ -7625,7 +7625,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57">
         <v>6576.5</v>
@@ -7670,7 +7670,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ACF60EB-3688-4D99-8212-ADE8011CFC68}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D8C0481-DF0B-4455-8FD9-668B812E23E8}">
   <dimension ref="A2:N57"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -7681,73 +7681,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>54.4</v>
@@ -7765,7 +7765,7 @@
         <v>53.9</v>
       </c>
       <c r="H10">
-        <v>182</v>
+        <v>182.1</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -7774,7 +7774,7 @@
         <v>67.900000000000006</v>
       </c>
       <c r="K10">
-        <v>61.6</v>
+        <v>61.7</v>
       </c>
       <c r="L10">
         <v>18.2</v>
@@ -7788,10 +7788,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>14.5</v>
@@ -7832,10 +7832,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>47.4</v>
@@ -7844,7 +7844,7 @@
         <v>24.4</v>
       </c>
       <c r="E12">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="F12">
         <v>42.1</v>
@@ -7853,7 +7853,7 @@
         <v>23.7</v>
       </c>
       <c r="H12">
-        <v>18.600000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="I12">
         <v>0.1</v>
@@ -7871,15 +7871,15 @@
         <v>30.7</v>
       </c>
       <c r="N12">
-        <v>66.7</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>34.200000000000003</v>
@@ -7897,7 +7897,7 @@
         <v>38.799999999999997</v>
       </c>
       <c r="H13">
-        <v>64.400000000000006</v>
+        <v>64.5</v>
       </c>
       <c r="I13">
         <v>0.1</v>
@@ -7915,15 +7915,15 @@
         <v>26.3</v>
       </c>
       <c r="N13">
-        <v>40.9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>3.4</v>
@@ -7932,7 +7932,7 @@
         <v>89.8</v>
       </c>
       <c r="E14">
-        <v>152.30000000000001</v>
+        <v>152.4</v>
       </c>
       <c r="F14">
         <v>1.8</v>
@@ -7959,15 +7959,15 @@
         <v>89.6</v>
       </c>
       <c r="N14">
-        <v>131</v>
+        <v>131.1</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>34.9</v>
@@ -8008,10 +8008,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>7.6</v>
@@ -8052,10 +8052,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>32.200000000000003</v>
@@ -8073,7 +8073,7 @@
         <v>61.2</v>
       </c>
       <c r="H17">
-        <v>85.9</v>
+        <v>85.8</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -8096,10 +8096,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>268.39999999999998</v>
@@ -8114,7 +8114,7 @@
         <v>237.1</v>
       </c>
       <c r="G18">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="H18">
         <v>9.8000000000000007</v>
@@ -8140,10 +8140,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>234.6</v>
@@ -8184,10 +8184,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>158.80000000000001</v>
@@ -8228,16 +8228,16 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>66.8</v>
       </c>
       <c r="D21">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="E21">
         <v>49.3</v>
@@ -8249,7 +8249,7 @@
         <v>20.9</v>
       </c>
       <c r="H21">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="I21">
         <v>0.7</v>
@@ -8267,15 +8267,15 @@
         <v>50.9</v>
       </c>
       <c r="N21">
-        <v>66.099999999999994</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>26.2</v>
@@ -8284,7 +8284,7 @@
         <v>61.2</v>
       </c>
       <c r="E22">
-        <v>93.7</v>
+        <v>93.8</v>
       </c>
       <c r="F22">
         <v>21.5</v>
@@ -8293,7 +8293,7 @@
         <v>65.599999999999994</v>
       </c>
       <c r="H22">
-        <v>85.8</v>
+        <v>85.9</v>
       </c>
       <c r="I22">
         <v>1.2</v>
@@ -8311,15 +8311,15 @@
         <v>54.7</v>
       </c>
       <c r="N22">
-        <v>174.8</v>
+        <v>174.9</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>17.3</v>
@@ -8360,10 +8360,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>139</v>
@@ -8404,10 +8404,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.7</v>
@@ -8416,7 +8416,7 @@
         <v>40.9</v>
       </c>
       <c r="E25">
-        <v>71.099999999999994</v>
+        <v>70.8</v>
       </c>
       <c r="F25">
         <v>34.200000000000003</v>
@@ -8425,7 +8425,7 @@
         <v>53</v>
       </c>
       <c r="H25">
-        <v>92.6</v>
+        <v>92.2</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -8448,10 +8448,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>28.7</v>
@@ -8460,7 +8460,7 @@
         <v>27.8</v>
       </c>
       <c r="E26">
-        <v>82.5</v>
+        <v>81.8</v>
       </c>
       <c r="F26">
         <v>22.3</v>
@@ -8469,7 +8469,7 @@
         <v>31.2</v>
       </c>
       <c r="H26">
-        <v>102.1</v>
+        <v>101.2</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -8487,15 +8487,15 @@
         <v>15.9</v>
       </c>
       <c r="N26">
-        <v>15</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.5</v>
@@ -8536,10 +8536,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -8548,7 +8548,7 @@
         <v>61.2</v>
       </c>
       <c r="E28">
-        <v>162.80000000000001</v>
+        <v>162.9</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -8575,15 +8575,15 @@
         <v>87.9</v>
       </c>
       <c r="N28">
-        <v>192</v>
+        <v>192.1</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>11.4</v>
@@ -8619,33 +8619,33 @@
         <v>98.1</v>
       </c>
       <c r="N29">
-        <v>709.7</v>
+        <v>709.6</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>117.3</v>
       </c>
       <c r="D30">
-        <v>57.2</v>
+        <v>57.1</v>
       </c>
       <c r="E30">
-        <v>148</v>
+        <v>147.80000000000001</v>
       </c>
       <c r="F30">
         <v>98.3</v>
       </c>
       <c r="G30">
-        <v>63.6</v>
+        <v>63.5</v>
       </c>
       <c r="H30">
-        <v>167.4</v>
+        <v>167.2</v>
       </c>
       <c r="I30">
         <v>0.1</v>
@@ -8668,10 +8668,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>45</v>
@@ -8712,28 +8712,28 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>96.9</v>
       </c>
       <c r="D32">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="E32">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
       <c r="F32">
         <v>75.400000000000006</v>
       </c>
       <c r="G32">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="H32">
-        <v>35.299999999999997</v>
+        <v>35.5</v>
       </c>
       <c r="I32">
         <v>0.9</v>
@@ -8751,15 +8751,15 @@
         <v>31.9</v>
       </c>
       <c r="N32">
-        <v>81.7</v>
+        <v>81.900000000000006</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>24.1</v>
@@ -8800,10 +8800,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>13.4</v>
@@ -8821,7 +8821,7 @@
         <v>71.900000000000006</v>
       </c>
       <c r="H34">
-        <v>160.69999999999999</v>
+        <v>160.80000000000001</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -8830,7 +8830,7 @@
         <v>61.4</v>
       </c>
       <c r="K34">
-        <v>91.2</v>
+        <v>91.3</v>
       </c>
       <c r="L34">
         <v>1.6</v>
@@ -8844,10 +8844,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>235.1</v>
@@ -8888,10 +8888,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>357.4</v>
@@ -8932,7 +8932,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>2115.1</v>
@@ -8973,10 +8973,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>17.399999999999999</v>
@@ -9012,24 +9012,24 @@
         <v>50.8</v>
       </c>
       <c r="N38">
-        <v>113</v>
+        <v>113.1</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>11.1</v>
       </c>
       <c r="D39">
-        <v>96.2</v>
+        <v>97.2</v>
       </c>
       <c r="E39">
-        <v>384.4</v>
+        <v>395.4</v>
       </c>
       <c r="F39">
         <v>4.3</v>
@@ -9038,33 +9038,33 @@
         <v>97</v>
       </c>
       <c r="H39">
-        <v>274.3</v>
+        <v>288.89999999999998</v>
       </c>
       <c r="I39">
         <v>0.5</v>
       </c>
       <c r="J39">
-        <v>66.400000000000006</v>
+        <v>81.5</v>
       </c>
       <c r="K39">
-        <v>189.1</v>
+        <v>196.6</v>
       </c>
       <c r="L39">
         <v>6.3</v>
       </c>
       <c r="M39">
-        <v>98</v>
+        <v>98.4</v>
       </c>
       <c r="N39">
-        <v>473.7</v>
+        <v>482.6</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>28.1</v>
@@ -9073,7 +9073,7 @@
         <v>91.6</v>
       </c>
       <c r="E40">
-        <v>314.8</v>
+        <v>328.8</v>
       </c>
       <c r="F40">
         <v>14.5</v>
@@ -9082,16 +9082,16 @@
         <v>88.1</v>
       </c>
       <c r="H40">
-        <v>261.89999999999998</v>
+        <v>278.2</v>
       </c>
       <c r="I40">
         <v>0.6</v>
       </c>
       <c r="J40">
-        <v>31.3</v>
+        <v>31.5</v>
       </c>
       <c r="K40">
-        <v>34.9</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="L40">
         <v>13</v>
@@ -9100,33 +9100,33 @@
         <v>98.1</v>
       </c>
       <c r="N40">
-        <v>385.8</v>
+        <v>397.6</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>117.2</v>
       </c>
       <c r="D41">
-        <v>87.1</v>
+        <v>86.6</v>
       </c>
       <c r="E41">
-        <v>312.39999999999998</v>
+        <v>301.39999999999998</v>
       </c>
       <c r="F41">
         <v>108.8</v>
       </c>
       <c r="G41">
-        <v>87.8</v>
+        <v>87.4</v>
       </c>
       <c r="H41">
-        <v>321.10000000000002</v>
+        <v>309.8</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -9141,18 +9141,18 @@
         <v>8.4</v>
       </c>
       <c r="M41">
-        <v>77.400000000000006</v>
+        <v>76.5</v>
       </c>
       <c r="N41">
-        <v>199.9</v>
+        <v>193.5</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>33.6</v>
@@ -9170,7 +9170,7 @@
         <v>26.3</v>
       </c>
       <c r="H42">
-        <v>36.299999999999997</v>
+        <v>36.4</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -9193,37 +9193,37 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>49.2</v>
       </c>
       <c r="D43">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="E43">
-        <v>120.7</v>
+        <v>115.6</v>
       </c>
       <c r="F43">
         <v>35.4</v>
       </c>
       <c r="G43">
-        <v>54.7</v>
+        <v>53.3</v>
       </c>
       <c r="H43">
-        <v>98.4</v>
+        <v>92.1</v>
       </c>
       <c r="I43">
         <v>0</v>
       </c>
       <c r="J43">
-        <v>68.599999999999994</v>
+        <v>73</v>
       </c>
       <c r="K43">
-        <v>82.9</v>
+        <v>83.2</v>
       </c>
       <c r="L43">
         <v>13.8</v>
@@ -9232,15 +9232,15 @@
         <v>83.7</v>
       </c>
       <c r="N43">
-        <v>178.2</v>
+        <v>176.2</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>58.6</v>
@@ -9281,10 +9281,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>5.9</v>
@@ -9325,10 +9325,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>15.5</v>
@@ -9364,33 +9364,33 @@
         <v>22.9</v>
       </c>
       <c r="N46">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>4.3</v>
       </c>
       <c r="D47">
-        <v>75.8</v>
+        <v>83.9</v>
       </c>
       <c r="E47">
-        <v>67.400000000000006</v>
+        <v>74.400000000000006</v>
       </c>
       <c r="F47">
         <v>4.2</v>
       </c>
       <c r="G47">
-        <v>76.099999999999994</v>
+        <v>84.3</v>
       </c>
       <c r="H47">
-        <v>66</v>
+        <v>73.099999999999994</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -9408,15 +9408,15 @@
         <v>63.1</v>
       </c>
       <c r="N47">
-        <v>145.4</v>
+        <v>148.5</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>10.7</v>
@@ -9457,16 +9457,16 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>209.4</v>
       </c>
       <c r="D49">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="E49">
         <v>6.1</v>
@@ -9475,19 +9475,19 @@
         <v>112.8</v>
       </c>
       <c r="G49">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="H49">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="I49">
         <v>1.3</v>
       </c>
       <c r="J49">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="K49">
-        <v>5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="L49">
         <v>95.3</v>
@@ -9501,10 +9501,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>3323.8</v>
@@ -9513,7 +9513,7 @@
         <v>23.5</v>
       </c>
       <c r="E50">
-        <v>42.9</v>
+        <v>43.5</v>
       </c>
       <c r="F50">
         <v>2690.2</v>
@@ -9522,7 +9522,7 @@
         <v>27.6</v>
       </c>
       <c r="H50">
-        <v>50.4</v>
+        <v>51.1</v>
       </c>
       <c r="I50">
         <v>21.2</v>
@@ -9537,18 +9537,18 @@
         <v>612.4</v>
       </c>
       <c r="M50">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="N50">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>33.200000000000003</v>
@@ -9557,7 +9557,7 @@
         <v>46.9</v>
       </c>
       <c r="E51">
-        <v>136.1</v>
+        <v>136.19999999999999</v>
       </c>
       <c r="F51">
         <v>28.3</v>
@@ -9566,7 +9566,7 @@
         <v>46.1</v>
       </c>
       <c r="H51">
-        <v>137.30000000000001</v>
+        <v>137.4</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -9584,15 +9584,15 @@
         <v>51.9</v>
       </c>
       <c r="N51">
-        <v>129.6</v>
+        <v>129.69999999999999</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>22.3</v>
@@ -9633,10 +9633,10 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53">
         <v>310</v>
@@ -9645,7 +9645,7 @@
         <v>76.900000000000006</v>
       </c>
       <c r="E53">
-        <v>378.2</v>
+        <v>378.4</v>
       </c>
       <c r="F53">
         <v>196.2</v>
@@ -9654,7 +9654,7 @@
         <v>82.7</v>
       </c>
       <c r="H53">
-        <v>452.2</v>
+        <v>452.3</v>
       </c>
       <c r="I53">
         <v>1.2</v>
@@ -9663,7 +9663,7 @@
         <v>22</v>
       </c>
       <c r="K53">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="L53">
         <v>112.5</v>
@@ -9672,33 +9672,33 @@
         <v>67.5</v>
       </c>
       <c r="N53">
-        <v>252.7</v>
+        <v>252.9</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54">
         <v>147.69999999999999</v>
       </c>
       <c r="D54">
-        <v>59.5</v>
+        <v>59.9</v>
       </c>
       <c r="E54">
-        <v>137</v>
+        <v>138.9</v>
       </c>
       <c r="F54">
         <v>141.19999999999999</v>
       </c>
       <c r="G54">
-        <v>58.6</v>
+        <v>59</v>
       </c>
       <c r="H54">
-        <v>137.1</v>
+        <v>139.1</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -9716,15 +9716,15 @@
         <v>80.7</v>
       </c>
       <c r="N54">
-        <v>135.19999999999999</v>
+        <v>136.4</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C55">
         <v>63.6</v>
@@ -9765,7 +9765,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C56">
         <v>4461.3999999999996</v>
@@ -9774,7 +9774,7 @@
         <v>30.5</v>
       </c>
       <c r="E56">
-        <v>79.7</v>
+        <v>80</v>
       </c>
       <c r="F56">
         <v>3437.8</v>
@@ -9783,16 +9783,16 @@
         <v>34.4</v>
       </c>
       <c r="H56">
-        <v>88.1</v>
+        <v>88.4</v>
       </c>
       <c r="I56">
         <v>26.3</v>
       </c>
       <c r="J56">
-        <v>4.4000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="K56">
-        <v>8.1</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="L56">
         <v>997.4</v>
@@ -9801,12 +9801,12 @@
         <v>17.8</v>
       </c>
       <c r="N56">
-        <v>52.5</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57">
         <v>6576.5</v>
@@ -9815,7 +9815,7 @@
         <v>32.5</v>
       </c>
       <c r="E57">
-        <v>86.2</v>
+        <v>86.4</v>
       </c>
       <c r="F57">
         <v>5027.7</v>
@@ -9824,16 +9824,16 @@
         <v>35.4</v>
       </c>
       <c r="H57">
-        <v>92.9</v>
+        <v>93.1</v>
       </c>
       <c r="I57">
         <v>34.6</v>
       </c>
       <c r="J57">
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="K57">
-        <v>9</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="L57">
         <v>1514.3</v>
@@ -9842,7 +9842,7 @@
         <v>23.7</v>
       </c>
       <c r="N57">
-        <v>65.7</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -9862,73 +9862,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>54.4</v>
@@ -9969,10 +9969,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>14.5</v>
@@ -10013,10 +10013,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>47.4</v>
@@ -10057,10 +10057,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>34.200000000000003</v>
@@ -10101,10 +10101,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>3.4</v>
@@ -10145,10 +10145,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>34.9</v>
@@ -10189,10 +10189,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>7.6</v>
@@ -10233,10 +10233,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>32.200000000000003</v>
@@ -10277,10 +10277,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>268.39999999999998</v>
@@ -10321,10 +10321,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>234.6</v>
@@ -10365,10 +10365,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>158.80000000000001</v>
@@ -10409,10 +10409,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>66.8</v>
@@ -10453,10 +10453,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>26.2</v>
@@ -10497,10 +10497,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>17.3</v>
@@ -10541,10 +10541,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>139</v>
@@ -10585,10 +10585,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.7</v>
@@ -10629,10 +10629,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>28.7</v>
@@ -10673,10 +10673,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.5</v>
@@ -10717,10 +10717,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -10761,10 +10761,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>11.4</v>
@@ -10805,10 +10805,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>117.3</v>
@@ -10849,10 +10849,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>45</v>
@@ -10893,10 +10893,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>96.9</v>
@@ -10937,10 +10937,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>24.1</v>
@@ -10981,10 +10981,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>13.4</v>
@@ -11025,10 +11025,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>235.1</v>
@@ -11069,10 +11069,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>357.4</v>
@@ -11113,7 +11113,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>2115.1</v>
@@ -11154,10 +11154,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>17.399999999999999</v>
@@ -11198,10 +11198,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>11.1</v>
@@ -11242,10 +11242,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>28.1</v>
@@ -11286,10 +11286,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>117.2</v>
@@ -11330,10 +11330,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>33.6</v>
@@ -11374,10 +11374,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>49.2</v>
@@ -11418,10 +11418,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>58.6</v>
@@ -11462,10 +11462,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>5.9</v>
@@ -11506,10 +11506,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>15.5</v>
@@ -11550,10 +11550,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>4.3</v>
@@ -11594,10 +11594,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>10.7</v>
@@ -11638,10 +11638,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>209.4</v>
@@ -11682,10 +11682,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>3323.8</v>
@@ -11726,10 +11726,10 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>33.200000000000003</v>
@@ -11770,10 +11770,10 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>22.3</v>
@@ -11814,10 +11814,10 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53">
         <v>310</v>
@@ -11858,10 +11858,10 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54">
         <v>147.69999999999999</v>
@@ -11902,10 +11902,10 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C55">
         <v>63.6</v>
@@ -11946,7 +11946,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C56">
         <v>4461.3999999999996</v>
@@ -11987,7 +11987,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57">
         <v>6576.5</v>
@@ -12043,73 +12043,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>54.4</v>
@@ -12150,10 +12150,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>14.5</v>
@@ -12194,10 +12194,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>47.4</v>
@@ -12238,10 +12238,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>34.200000000000003</v>
@@ -12282,10 +12282,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>3.4</v>
@@ -12326,10 +12326,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>34.9</v>
@@ -12370,10 +12370,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>7.6</v>
@@ -12414,10 +12414,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>32.200000000000003</v>
@@ -12458,10 +12458,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>268.39999999999998</v>
@@ -12502,10 +12502,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>234.6</v>
@@ -12546,10 +12546,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>158.80000000000001</v>
@@ -12590,10 +12590,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>66.8</v>
@@ -12634,10 +12634,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>26.2</v>
@@ -12678,10 +12678,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>17.3</v>
@@ -12722,10 +12722,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>139</v>
@@ -12766,10 +12766,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.7</v>
@@ -12810,10 +12810,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>28.7</v>
@@ -12854,10 +12854,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.5</v>
@@ -12898,10 +12898,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -12942,10 +12942,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>11.4</v>
@@ -12986,10 +12986,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>117.3</v>
@@ -13030,10 +13030,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>45</v>
@@ -13074,10 +13074,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>96.9</v>
@@ -13118,10 +13118,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>24.1</v>
@@ -13162,10 +13162,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>13.4</v>
@@ -13206,10 +13206,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>235.1</v>
@@ -13250,10 +13250,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>357.4</v>
@@ -13294,7 +13294,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>2115.1</v>
@@ -13335,10 +13335,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>17.399999999999999</v>
@@ -13379,10 +13379,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>11.1</v>
@@ -13423,10 +13423,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>28.1</v>
@@ -13467,10 +13467,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>117.2</v>
@@ -13511,10 +13511,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>33.6</v>
@@ -13555,10 +13555,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>49.2</v>
@@ -13599,10 +13599,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>58.6</v>
@@ -13643,10 +13643,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>5.9</v>
@@ -13687,10 +13687,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>15.5</v>
@@ -13731,10 +13731,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>4.3</v>
@@ -13775,10 +13775,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>10.7</v>
@@ -13819,10 +13819,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>209.4</v>
@@ -13863,10 +13863,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>3323.8</v>
@@ -13907,10 +13907,10 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>33.200000000000003</v>
@@ -13951,10 +13951,10 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>22.3</v>
@@ -13995,10 +13995,10 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53">
         <v>310</v>
@@ -14039,10 +14039,10 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54">
         <v>147.69999999999999</v>
@@ -14083,10 +14083,10 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C55">
         <v>63.6</v>
@@ -14127,7 +14127,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C56">
         <v>4461.3999999999996</v>
@@ -14168,7 +14168,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57">
         <v>6576.5</v>
@@ -14224,73 +14224,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>54.4</v>
@@ -14331,10 +14331,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>14.5</v>
@@ -14375,10 +14375,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>47.4</v>
@@ -14419,10 +14419,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>34.200000000000003</v>
@@ -14463,10 +14463,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>3.4</v>
@@ -14507,10 +14507,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>34.9</v>
@@ -14551,10 +14551,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>7.6</v>
@@ -14595,10 +14595,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>32.200000000000003</v>
@@ -14639,10 +14639,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>268.39999999999998</v>
@@ -14683,10 +14683,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>234.6</v>
@@ -14727,10 +14727,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>158.80000000000001</v>
@@ -14771,10 +14771,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>66.8</v>
@@ -14815,10 +14815,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>26.2</v>
@@ -14859,10 +14859,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>17.3</v>
@@ -14903,10 +14903,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>139</v>
@@ -14947,10 +14947,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.7</v>
@@ -14991,10 +14991,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>28.7</v>
@@ -15035,10 +15035,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.5</v>
@@ -15079,10 +15079,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -15123,10 +15123,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>11.4</v>
@@ -15167,10 +15167,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>117.3</v>
@@ -15211,10 +15211,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>45</v>
@@ -15255,10 +15255,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>96.9</v>
@@ -15299,10 +15299,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>24.1</v>
@@ -15343,10 +15343,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>13.4</v>
@@ -15387,10 +15387,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>235.1</v>
@@ -15431,10 +15431,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>357.4</v>
@@ -15475,7 +15475,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>2115.1</v>
@@ -15516,10 +15516,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>17.399999999999999</v>
@@ -15560,10 +15560,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>11.1</v>
@@ -15604,10 +15604,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>28.1</v>
@@ -15648,10 +15648,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>117.2</v>
@@ -15692,10 +15692,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>33.6</v>
@@ -15736,10 +15736,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>49.2</v>
@@ -15780,10 +15780,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>58.6</v>
@@ -15824,10 +15824,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>5.9</v>
@@ -15868,10 +15868,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>15.5</v>
@@ -15912,10 +15912,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>4.3</v>
@@ -15956,10 +15956,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>10.7</v>
@@ -16000,10 +16000,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>209.4</v>
@@ -16044,10 +16044,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>3323.8</v>
@@ -16088,10 +16088,10 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>33.200000000000003</v>
@@ -16132,10 +16132,10 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>22.3</v>
@@ -16176,10 +16176,10 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53">
         <v>310</v>
@@ -16220,10 +16220,10 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54">
         <v>147.69999999999999</v>
@@ -16264,10 +16264,10 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C55">
         <v>63.6</v>
@@ -16308,7 +16308,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C56">
         <v>4461.3999999999996</v>
@@ -16349,7 +16349,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57">
         <v>6576.5</v>
@@ -16405,73 +16405,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>54.4</v>
@@ -16512,10 +16512,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>14.5</v>
@@ -16556,10 +16556,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>47.4</v>
@@ -16600,10 +16600,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>34.200000000000003</v>
@@ -16644,10 +16644,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>3.4</v>
@@ -16688,10 +16688,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>34.9</v>
@@ -16732,10 +16732,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>7.6</v>
@@ -16776,10 +16776,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>32.200000000000003</v>
@@ -16820,10 +16820,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>268.39999999999998</v>
@@ -16864,10 +16864,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>234.6</v>
@@ -16908,10 +16908,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>158.80000000000001</v>
@@ -16952,10 +16952,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>66.8</v>
@@ -16996,10 +16996,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>26.2</v>
@@ -17040,10 +17040,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>17.3</v>
@@ -17084,10 +17084,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>139</v>
@@ -17128,10 +17128,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.7</v>
@@ -17172,10 +17172,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>28.7</v>
@@ -17216,10 +17216,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.5</v>
@@ -17260,10 +17260,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -17304,10 +17304,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>11.4</v>
@@ -17348,10 +17348,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>117.3</v>
@@ -17392,10 +17392,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>45</v>
@@ -17436,10 +17436,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>96.9</v>
@@ -17480,10 +17480,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>24.1</v>
@@ -17524,10 +17524,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>13.4</v>
@@ -17568,10 +17568,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>235.1</v>
@@ -17612,10 +17612,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>357.4</v>
@@ -17656,7 +17656,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>2115.1</v>
@@ -17697,10 +17697,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>17.399999999999999</v>
@@ -17741,10 +17741,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>11.1</v>
@@ -17785,10 +17785,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>28.1</v>
@@ -17829,10 +17829,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>117.2</v>
@@ -17873,10 +17873,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>33.6</v>
@@ -17917,10 +17917,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>49.2</v>
@@ -17961,10 +17961,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>58.6</v>
@@ -18005,10 +18005,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>5.9</v>
@@ -18049,10 +18049,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>15.5</v>
@@ -18093,10 +18093,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>4.3</v>
@@ -18137,10 +18137,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>10.7</v>
@@ -18181,10 +18181,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>209.4</v>
@@ -18225,10 +18225,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>3323.8</v>
@@ -18269,10 +18269,10 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>33.200000000000003</v>
@@ -18313,10 +18313,10 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>22.3</v>
@@ -18357,10 +18357,10 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53">
         <v>310</v>
@@ -18401,10 +18401,10 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54">
         <v>147.69999999999999</v>
@@ -18445,10 +18445,10 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C55">
         <v>63.6</v>
@@ -18489,7 +18489,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C56">
         <v>4461.3999999999996</v>
@@ -18530,7 +18530,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57">
         <v>6576.5</v>
@@ -18586,73 +18586,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>54.4</v>
@@ -18693,10 +18693,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>14.5</v>
@@ -18737,10 +18737,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>47.4</v>
@@ -18781,10 +18781,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>34.200000000000003</v>
@@ -18825,10 +18825,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>3.4</v>
@@ -18869,10 +18869,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>34.9</v>
@@ -18913,10 +18913,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>7.6</v>
@@ -18957,10 +18957,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>32.200000000000003</v>
@@ -19001,10 +19001,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>268.39999999999998</v>
@@ -19045,10 +19045,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>234.6</v>
@@ -19089,10 +19089,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>158.80000000000001</v>
@@ -19133,10 +19133,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>66.8</v>
@@ -19177,10 +19177,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>26.2</v>
@@ -19221,10 +19221,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>17.3</v>
@@ -19265,10 +19265,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>139</v>
@@ -19309,10 +19309,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.7</v>
@@ -19353,10 +19353,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>28.7</v>
@@ -19397,10 +19397,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.5</v>
@@ -19441,10 +19441,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -19485,10 +19485,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>11.4</v>
@@ -19529,10 +19529,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>117.3</v>
@@ -19573,10 +19573,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>45</v>
@@ -19617,10 +19617,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>96.9</v>
@@ -19661,10 +19661,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>24.1</v>
@@ -19705,10 +19705,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>13.4</v>
@@ -19749,10 +19749,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>235.1</v>
@@ -19793,10 +19793,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>357.4</v>
@@ -19837,7 +19837,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>2115.1</v>
@@ -19878,10 +19878,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>17.399999999999999</v>
@@ -19922,10 +19922,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>11.1</v>
@@ -19966,10 +19966,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>28.1</v>
@@ -20010,10 +20010,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>117.2</v>
@@ -20054,10 +20054,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>33.6</v>
@@ -20098,10 +20098,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>49.2</v>
@@ -20142,10 +20142,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>58.6</v>
@@ -20186,10 +20186,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>5.9</v>
@@ -20230,10 +20230,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>15.5</v>
@@ -20274,10 +20274,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>4.3</v>
@@ -20318,10 +20318,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>10.7</v>
@@ -20362,10 +20362,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>209.4</v>
@@ -20406,10 +20406,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>3323.8</v>
@@ -20450,10 +20450,10 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>33.200000000000003</v>
@@ -20494,10 +20494,10 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>22.3</v>
@@ -20538,10 +20538,10 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53">
         <v>310</v>
@@ -20582,10 +20582,10 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54">
         <v>147.69999999999999</v>
@@ -20626,10 +20626,10 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C55">
         <v>63.6</v>
@@ -20670,7 +20670,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C56">
         <v>4461.3999999999996</v>
@@ -20711,7 +20711,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57">
         <v>6576.5</v>
@@ -20767,73 +20767,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>54.4</v>
@@ -20874,10 +20874,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>14.5</v>
@@ -20918,10 +20918,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>47.4</v>
@@ -20962,10 +20962,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>34.200000000000003</v>
@@ -21006,10 +21006,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>3.4</v>
@@ -21050,10 +21050,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>34.9</v>
@@ -21094,10 +21094,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>7.6</v>
@@ -21138,10 +21138,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>32.200000000000003</v>
@@ -21182,10 +21182,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>268.39999999999998</v>
@@ -21226,10 +21226,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>234.6</v>
@@ -21270,10 +21270,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>158.80000000000001</v>
@@ -21314,10 +21314,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>66.8</v>
@@ -21358,10 +21358,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>26.2</v>
@@ -21402,10 +21402,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>17.3</v>
@@ -21446,10 +21446,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>139</v>
@@ -21490,10 +21490,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.7</v>
@@ -21534,10 +21534,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>28.7</v>
@@ -21578,10 +21578,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.5</v>
@@ -21622,10 +21622,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -21666,10 +21666,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>11.4</v>
@@ -21710,10 +21710,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>117.3</v>
@@ -21754,10 +21754,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>45</v>
@@ -21798,10 +21798,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>96.9</v>
@@ -21842,10 +21842,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>24.1</v>
@@ -21886,10 +21886,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>13.4</v>
@@ -21930,10 +21930,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>235.1</v>
@@ -21974,10 +21974,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>357.4</v>
@@ -22018,7 +22018,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>2115.1</v>
@@ -22059,10 +22059,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>17.399999999999999</v>
@@ -22103,10 +22103,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>11.1</v>
@@ -22147,10 +22147,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>28.1</v>
@@ -22191,10 +22191,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>117.2</v>
@@ -22235,10 +22235,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>33.6</v>
@@ -22279,10 +22279,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>49.2</v>
@@ -22323,10 +22323,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>58.6</v>
@@ -22367,10 +22367,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>5.9</v>
@@ -22411,10 +22411,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>15.5</v>
@@ -22455,10 +22455,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>4.3</v>
@@ -22499,10 +22499,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>10.7</v>
@@ -22543,10 +22543,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>209.4</v>
@@ -22587,10 +22587,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>3323.8</v>
@@ -22631,10 +22631,10 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>33.200000000000003</v>
@@ -22675,10 +22675,10 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>22.3</v>
@@ -22719,10 +22719,10 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53">
         <v>310</v>
@@ -22763,10 +22763,10 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54">
         <v>147.69999999999999</v>
@@ -22807,10 +22807,10 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C55">
         <v>63.6</v>
@@ -22851,7 +22851,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C56">
         <v>4461.3999999999996</v>
@@ -22892,7 +22892,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57">
         <v>6576.5</v>
@@ -22948,73 +22948,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>54.4</v>
@@ -23055,10 +23055,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>14.5</v>
@@ -23099,10 +23099,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>47.4</v>
@@ -23143,10 +23143,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>34.200000000000003</v>
@@ -23187,10 +23187,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>3.4</v>
@@ -23231,10 +23231,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>34.9</v>
@@ -23275,10 +23275,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>7.6</v>
@@ -23319,10 +23319,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>32.200000000000003</v>
@@ -23363,10 +23363,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>268.39999999999998</v>
@@ -23407,10 +23407,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>234.6</v>
@@ -23451,10 +23451,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>158.80000000000001</v>
@@ -23495,10 +23495,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>66.8</v>
@@ -23539,10 +23539,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>26.2</v>
@@ -23583,10 +23583,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>17.3</v>
@@ -23627,10 +23627,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>139</v>
@@ -23671,10 +23671,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.7</v>
@@ -23715,10 +23715,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>28.7</v>
@@ -23759,10 +23759,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.5</v>
@@ -23803,10 +23803,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -23847,10 +23847,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>11.4</v>
@@ -23891,10 +23891,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>117.3</v>
@@ -23935,10 +23935,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>45</v>
@@ -23979,10 +23979,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>96.9</v>
@@ -24023,10 +24023,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>24.1</v>
@@ -24067,10 +24067,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>13.4</v>
@@ -24111,10 +24111,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>235.1</v>
@@ -24155,10 +24155,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>357.4</v>
@@ -24199,7 +24199,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>2115.1</v>
@@ -24240,10 +24240,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>17.399999999999999</v>
@@ -24284,10 +24284,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>11.1</v>
@@ -24328,10 +24328,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>28.1</v>
@@ -24372,10 +24372,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>117.2</v>
@@ -24416,10 +24416,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>33.6</v>
@@ -24460,10 +24460,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>49.2</v>
@@ -24504,10 +24504,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>58.6</v>
@@ -24548,10 +24548,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>5.9</v>
@@ -24592,10 +24592,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>15.5</v>
@@ -24636,10 +24636,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>4.3</v>
@@ -24680,10 +24680,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>10.7</v>
@@ -24724,10 +24724,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>209.4</v>
@@ -24768,10 +24768,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>3323.8</v>
@@ -24812,10 +24812,10 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>33.200000000000003</v>
@@ -24856,10 +24856,10 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>22.3</v>
@@ -24900,10 +24900,10 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53">
         <v>310</v>
@@ -24944,10 +24944,10 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54">
         <v>147.69999999999999</v>
@@ -24988,10 +24988,10 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C55">
         <v>63.6</v>
@@ -25032,7 +25032,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C56">
         <v>4461.3999999999996</v>
@@ -25073,7 +25073,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57">
         <v>6576.5</v>
@@ -25129,73 +25129,73 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>15</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>54.4</v>
@@ -25236,10 +25236,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>14.5</v>
@@ -25280,10 +25280,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>47.4</v>
@@ -25324,10 +25324,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>34.200000000000003</v>
@@ -25368,10 +25368,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>3.4</v>
@@ -25412,10 +25412,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>34.9</v>
@@ -25456,10 +25456,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>7.6</v>
@@ -25500,10 +25500,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>32.200000000000003</v>
@@ -25544,10 +25544,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>268.39999999999998</v>
@@ -25588,10 +25588,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>234.6</v>
@@ -25632,10 +25632,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>158.80000000000001</v>
@@ -25676,10 +25676,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>66.8</v>
@@ -25720,10 +25720,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>26.2</v>
@@ -25764,10 +25764,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>17.3</v>
@@ -25808,10 +25808,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>139</v>
@@ -25852,10 +25852,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>44.7</v>
@@ -25896,10 +25896,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>28.7</v>
@@ -25940,10 +25940,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1.5</v>
@@ -25984,10 +25984,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -26028,10 +26028,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>11.4</v>
@@ -26072,10 +26072,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>117.3</v>
@@ -26116,10 +26116,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>45</v>
@@ -26160,10 +26160,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>96.9</v>
@@ -26204,10 +26204,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>24.1</v>
@@ -26248,10 +26248,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>13.4</v>
@@ -26292,10 +26292,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>235.1</v>
@@ -26336,10 +26336,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>357.4</v>
@@ -26380,7 +26380,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>2115.1</v>
@@ -26421,10 +26421,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
         <v>47</v>
-      </c>
-      <c r="B38" t="s">
-        <v>48</v>
       </c>
       <c r="C38">
         <v>17.399999999999999</v>
@@ -26465,10 +26465,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>11.1</v>
@@ -26509,10 +26509,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>28.1</v>
@@ -26553,10 +26553,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>117.2</v>
@@ -26597,10 +26597,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>33.6</v>
@@ -26641,10 +26641,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>49.2</v>
@@ -26685,10 +26685,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44">
         <v>58.6</v>
@@ -26729,10 +26729,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>5.9</v>
@@ -26773,10 +26773,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>15.5</v>
@@ -26817,10 +26817,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47">
         <v>4.3</v>
@@ -26861,10 +26861,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>10.7</v>
@@ -26905,10 +26905,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C49">
         <v>209.4</v>
@@ -26949,10 +26949,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>3323.8</v>
@@ -26993,10 +26993,10 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>33.200000000000003</v>
@@ -27037,10 +27037,10 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>22.3</v>
@@ -27081,10 +27081,10 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53">
         <v>310</v>
@@ -27125,10 +27125,10 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54">
         <v>147.69999999999999</v>
@@ -27169,10 +27169,10 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C55">
         <v>63.6</v>
@@ -27213,7 +27213,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C56">
         <v>4461.3999999999996</v>
@@ -27254,7 +27254,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57">
         <v>6576.5</v>
